--- a/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
@@ -86,10 +86,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -106,6 +109,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -479,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H21"/>
+  <dimension ref="A2:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -489,7 +495,10 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -508,24 +517,27 @@
       <c r="E3" s="3" t="n">
         <v>46255</v>
       </c>
+      <c r="H3" s="4" t="n">
+        <v>46262</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
@@ -546,27 +558,42 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>DaMai</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>SDB Properties Sdn Bhd</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>306</v>
       </c>
       <c r="E5" s="9" t="n"/>
@@ -577,23 +604,38 @@
         <f>F5/$D$5</f>
         <v/>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="H5" s="11">
+        <f>I5-F5</f>
+        <v/>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="J5" s="12">
+        <f>I5/$D$5</f>
+        <v/>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 54 units, Block B: 41 units</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Trinity Sensoria</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Trinity Group (Trinity Wellnessa &amp; Enlivea Dev S/B)</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>737</v>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -604,75 +646,96 @@
         <f>F6/$D$6</f>
         <v/>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="11">
+        <f>I6-F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>343</v>
+      </c>
+      <c r="J6" s="12">
+        <f>I6/$D$6</f>
+        <v/>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A1: 45 units, Block A2: 201 units, Block B: 97 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Ukay Spring</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Malton Berhad (Gapadu Harta S/B)</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>142</v>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="10" t="n"/>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Chin Hin Ulu Kelang</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Chin Hin Property (Melawati) S/B</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <v>1449</v>
       </c>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="10" t="n"/>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>LEA By The Hills</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>OSK Property (Jelang Vista S/B)</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="9" t="n">
         <v>344</v>
       </c>
       <c r="E9" s="9" t="n"/>
@@ -683,23 +746,38 @@
         <f>F9/$D$9</f>
         <v/>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="11">
+        <f>I9-F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>343</v>
+      </c>
+      <c r="J9" s="12">
+        <f>I9/$D$9</f>
+        <v/>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block L: 343 units</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Park One Residence</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Sime Darby Property (KL East) S/B</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="9" t="n">
         <v>234</v>
       </c>
       <c r="E10" s="9" t="n"/>
@@ -710,23 +788,34 @@
         <f>F10/$D$10</f>
         <v/>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="11">
+        <f>I10-F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>228</v>
+      </c>
+      <c r="J10" s="12">
+        <f>I10/$D$10</f>
+        <v/>
+      </c>
+      <c r="K10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Sierra Hijauan</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>IJM Land (Sierra Ukay S/B)</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>310</v>
       </c>
       <c r="E11" s="9" t="n"/>
@@ -737,23 +826,34 @@
         <f>F11/$D$11</f>
         <v/>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="11">
+        <f>I11-F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>273</v>
+      </c>
+      <c r="J11" s="12">
+        <f>I11/$D$11</f>
+        <v/>
+      </c>
+      <c r="K11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Embun @ Kemensah</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Titijaya Land Bhd (Aman Kemensah S/B)</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="9" t="n">
         <v>51</v>
       </c>
       <c r="E12" s="9" t="n"/>
@@ -764,27 +864,38 @@
         <f>F12/$D$12</f>
         <v/>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="11">
+        <f>I12-F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="J12" s="12">
+        <f>I12/$D$12</f>
+        <v/>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Emery not found on TEDUH</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Tijani Ukay Ampang</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Symphony Life Bhd (Ketapang Realty S/B)</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>118</v>
       </c>
       <c r="E13" s="9" t="n"/>
@@ -795,23 +906,34 @@
         <f>F13/$D$13</f>
         <v/>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="11">
+        <f>I13-F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="J13" s="12">
+        <f>I13/$D$13</f>
+        <v/>
+      </c>
+      <c r="K13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>19Trees</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>SDB Properties Sdn Bhd</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="9" t="n">
         <v>222</v>
       </c>
       <c r="E14" s="9" t="n"/>
@@ -822,23 +944,34 @@
         <f>F14/$D$14</f>
         <v/>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="11">
+        <f>I14-F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>222</v>
+      </c>
+      <c r="J14" s="12">
+        <f>I14/$D$14</f>
+        <v/>
+      </c>
+      <c r="K14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>20Trees</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>SDB Properties Sdn Bhd</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="9" t="n">
         <v>201</v>
       </c>
       <c r="E15" s="9" t="n"/>
@@ -849,27 +982,38 @@
         <f>F15/$D$15</f>
         <v/>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="11">
+        <f>I15-F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12">
+        <f>I15/$D$15</f>
+        <v/>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>No unit found on TEDUH</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Nadayu 63</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Nadayu Properties (Twin Ridge S/B)</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="9" t="n">
         <v>296</v>
       </c>
       <c r="E16" s="9" t="n"/>
@@ -880,23 +1024,38 @@
         <f>F16/$D$16</f>
         <v/>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="H16" s="11">
+        <f>I16-F16</f>
+        <v/>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>197</v>
+      </c>
+      <c r="J16" s="12">
+        <f>I16/$D$16</f>
+        <v/>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block B: 197 units</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>16 Quartz @ Taman Melawati</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Mitraland (Mitraland Melawati S/B)</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="9" t="n">
         <v>117</v>
       </c>
       <c r="E17" s="9" t="n"/>
@@ -907,23 +1066,34 @@
         <f>F17/$D$17</f>
         <v/>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="H17" s="11">
+        <f>I17-F17</f>
+        <v/>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="J17" s="12">
+        <f>I17/$D$17</f>
+        <v/>
+      </c>
+      <c r="K17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Trinity Wellnessa</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Trinity Group (Trinity Wellnessa &amp; Enlivea Dev S/B)</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="9" t="n">
         <v>463</v>
       </c>
       <c r="E18" s="9" t="n"/>
@@ -934,23 +1104,38 @@
         <f>F18/$D$18</f>
         <v/>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="11">
+        <f>I18-F18</f>
+        <v/>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>456</v>
+      </c>
+      <c r="J18" s="12">
+        <f>I18/$D$18</f>
+        <v/>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A1: 223 units, Block A2: 233 units</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Nassim Heights</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Newfield Holding (Nassim Development S/B)</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="9" t="n">
         <v>106</v>
       </c>
       <c r="E19" s="9" t="n"/>
@@ -961,23 +1146,34 @@
         <f>F19/$D$19</f>
         <v/>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="11">
+        <f>I19-F19</f>
+        <v/>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="J19" s="12">
+        <f>I19/$D$19</f>
+        <v/>
+      </c>
+      <c r="K19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Kelab Ukay Residence</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Sri Datai / Strong Heritage S/B</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="9" t="n">
         <v>15</v>
       </c>
       <c r="E20" s="9" t="n"/>
@@ -988,32 +1184,47 @@
         <f>F20/$D$20</f>
         <v/>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="11">
+        <f>I20-F20</f>
+        <v/>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="12">
+        <f>I20/$D$20</f>
+        <v/>
+      </c>
+      <c r="K20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Villaria</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="8" t="n">
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="10" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="H3:J3"/>
     <mergeCell ref="E3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="I5" s="11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J5" s="12">
         <f>I5/$D$5</f>
@@ -617,7 +617,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 54 units, Block B: 41 units</t>
+          <t>Latest sales - Block A: 54 units, Block B: 40 units</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
         <v/>
       </c>
       <c r="I6" s="11" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J6" s="12">
         <f>I6/$D$6</f>
@@ -659,7 +659,7 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Latest sales - Block A1: 45 units, Block A2: 201 units, Block B: 97 units</t>
+          <t>Latest sales - Block A1: 45 units, Block A2: 202 units, Block B: 100 units</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
@@ -493,7 +493,7 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>

--- a/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Ukay_Teduh_Weekly_Update.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L21"/>
+  <dimension ref="A2:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,10 @@
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -521,8 +524,11 @@
       <c r="F3" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="3" t="n">
         <v>46262</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -568,22 +574,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -617,20 +638,31 @@
         <f>G5/$D$5</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="10">
         <f>J5-G5</f>
         <v/>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="11">
         <f>J5/$D$5</f>
         <v/>
       </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 54 units, Block B: 40 units</t>
+      <c r="L5" s="12">
+        <f>M5-J5</f>
+        <v/>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="N5" s="13">
+        <f>M5/$D$5</f>
+        <v/>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 53 units, Block B: 40 units</t>
         </is>
       </c>
     </row>
@@ -662,20 +694,31 @@
         <f>G6/$D$6</f>
         <v/>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="10">
         <f>J6-G6</f>
         <v/>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="10" t="n">
         <v>347</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="11">
         <f>J6/$D$6</f>
         <v/>
       </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A1: 45 units, Block A2: 202 units, Block B: 100 units</t>
+      <c r="L6" s="12">
+        <f>M6-J6</f>
+        <v/>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>348</v>
+      </c>
+      <c r="N6" s="13">
+        <f>M6/$D$6</f>
+        <v/>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A1: 45 units, Block A2: 203 units, Block B: 100 units</t>
         </is>
       </c>
     </row>
@@ -700,10 +743,13 @@
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -730,10 +776,13 @@
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="10" t="n"/>
       <c r="H8" s="11" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -767,18 +816,29 @@
         <f>G9/$D$9</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="10">
         <f>J9-G9</f>
         <v/>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="10" t="n">
         <v>343</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="11">
         <f>J9/$D$9</f>
         <v/>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="12">
+        <f>M9-J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>343</v>
+      </c>
+      <c r="N9" s="13">
+        <f>M9/$D$9</f>
+        <v/>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block L: 343 units</t>
         </is>
@@ -812,18 +872,29 @@
         <f>G10/$D$10</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="10">
         <f>J10-G10</f>
         <v/>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="10" t="n">
         <v>228</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="11">
         <f>J10/$D$10</f>
         <v/>
       </c>
-      <c r="L10" s="8" t="inlineStr"/>
+      <c r="L10" s="12">
+        <f>M10-J10</f>
+        <v/>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="N10" s="13">
+        <f>M10/$D$10</f>
+        <v/>
+      </c>
+      <c r="O10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -853,18 +924,29 @@
         <f>G11/$D$11</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="10">
         <f>J11-G11</f>
         <v/>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="10" t="n">
         <v>273</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="11">
         <f>J11/$D$11</f>
         <v/>
       </c>
-      <c r="L11" s="8" t="inlineStr"/>
+      <c r="L11" s="12">
+        <f>M11-J11</f>
+        <v/>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="N11" s="13">
+        <f>M11/$D$11</f>
+        <v/>
+      </c>
+      <c r="O11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -894,18 +976,29 @@
         <f>G12/$D$12</f>
         <v/>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="10">
         <f>J12-G12</f>
         <v/>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="J12" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="11">
         <f>J12/$D$12</f>
         <v/>
       </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L12" s="12">
+        <f>M12-J12</f>
+        <v/>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="N12" s="13">
+        <f>M12/$D$12</f>
+        <v/>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>Emery not found on TEDUH</t>
         </is>
@@ -939,18 +1032,29 @@
         <f>G13/$D$13</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="10">
         <f>J13-G13</f>
         <v/>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="11">
         <f>J13/$D$13</f>
         <v/>
       </c>
-      <c r="L13" s="8" t="inlineStr"/>
+      <c r="L13" s="12">
+        <f>M13-J13</f>
+        <v/>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="N13" s="13">
+        <f>M13/$D$13</f>
+        <v/>
+      </c>
+      <c r="O13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -980,18 +1084,29 @@
         <f>G14/$D$14</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="10">
         <f>J14-G14</f>
         <v/>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" s="10" t="n">
         <v>222</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="11">
         <f>J14/$D$14</f>
         <v/>
       </c>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="L14" s="12">
+        <f>M14-J14</f>
+        <v/>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>222</v>
+      </c>
+      <c r="N14" s="13">
+        <f>M14/$D$14</f>
+        <v/>
+      </c>
+      <c r="O14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1021,18 +1136,29 @@
         <f>G15/$D$15</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="10">
         <f>J15-G15</f>
         <v/>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="11">
         <f>J15/$D$15</f>
         <v/>
       </c>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="L15" s="12">
+        <f>M15-J15</f>
+        <v/>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="13">
+        <f>M15/$D$15</f>
+        <v/>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>No unit found on TEDUH</t>
         </is>
@@ -1066,18 +1192,29 @@
         <f>G16/$D$16</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="10">
         <f>J16-G16</f>
         <v/>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="11">
         <f>J16/$D$16</f>
         <v/>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L16" s="12">
+        <f>M16-J16</f>
+        <v/>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="N16" s="13">
+        <f>M16/$D$16</f>
+        <v/>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block B: 197 units</t>
         </is>
@@ -1111,18 +1248,29 @@
         <f>G17/$D$17</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="10">
         <f>J17-G17</f>
         <v/>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="11">
         <f>J17/$D$17</f>
         <v/>
       </c>
-      <c r="L17" s="8" t="inlineStr"/>
+      <c r="L17" s="12">
+        <f>M17-J17</f>
+        <v/>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="N17" s="13">
+        <f>M17/$D$17</f>
+        <v/>
+      </c>
+      <c r="O17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1152,18 +1300,29 @@
         <f>G18/$D$18</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="10">
         <f>J18-G18</f>
         <v/>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J18" s="10" t="n">
         <v>456</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="11">
         <f>J18/$D$18</f>
         <v/>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L18" s="12">
+        <f>M18-J18</f>
+        <v/>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>456</v>
+      </c>
+      <c r="N18" s="13">
+        <f>M18/$D$18</f>
+        <v/>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A1: 223 units, Block A2: 233 units</t>
         </is>
@@ -1197,18 +1356,29 @@
         <f>G19/$D$19</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="10">
         <f>J19-G19</f>
         <v/>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="J19" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="11">
         <f>J19/$D$19</f>
         <v/>
       </c>
-      <c r="L19" s="8" t="inlineStr"/>
+      <c r="L19" s="12">
+        <f>M19-J19</f>
+        <v/>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="N19" s="13">
+        <f>M19/$D$19</f>
+        <v/>
+      </c>
+      <c r="O19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1238,18 +1408,29 @@
         <f>G20/$D$20</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="10">
         <f>J20-G20</f>
         <v/>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="J20" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="11">
         <f>J20/$D$20</f>
         <v/>
       </c>
-      <c r="L20" s="8" t="inlineStr"/>
+      <c r="L20" s="12">
+        <f>M20-J20</f>
+        <v/>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="13">
+        <f>M20/$D$20</f>
+        <v/>
+      </c>
+      <c r="O20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1268,19 +1449,23 @@
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="F3:H3"/>
+    <mergeCell ref="L3:N3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
